--- a/JsonConverter/ExcelFiles/InspectText.xlsx
+++ b/JsonConverter/ExcelFiles/InspectText.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30128"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{16243E1E-F831-423A-B8F9-24FFB712AB40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF012331-FB7D-4AB1-9B2B-12A4EA842F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>조사 텍스트 고유 ID</t>
   </si>
@@ -51,22 +51,85 @@
     <t>Description</t>
   </si>
   <si>
-    <t>inspect_note_start</t>
-  </si>
-  <si>
-    <t>피가 묻어 있는 정체불명의 쪽지이다.</t>
-  </si>
-  <si>
-    <t>inspect_note_description</t>
-  </si>
-  <si>
-    <t>어떤 내용이 적혀 있지만, 피 때문에 뒷부분을 알아볼 수 없다.</t>
-  </si>
-  <si>
-    <t>inspect_note_blood</t>
-  </si>
-  <si>
-    <t>노트의 피는 검게 말라붙어 있다. 흘린 지 오랜 시간이 지난 듯하다.</t>
+    <t>inspect_brokenframe_start</t>
+  </si>
+  <si>
+    <t>연구원들의 사진 같은데... 완전히 부서져서 잘 보이지 않는다.</t>
+  </si>
+  <si>
+    <t>inspect_brokenframe_harin</t>
+  </si>
+  <si>
+    <t>이 사람이 변이 사태의 유일한 생존자라고 들었는데, 아직 이 연구소에 남아 있는 걸까?</t>
+  </si>
+  <si>
+    <t>inspect_brokenframe_others</t>
+  </si>
+  <si>
+    <t>다른 연구원들이다. 현재는 변이체로 인해 모두 사망했다.</t>
+  </si>
+  <si>
+    <t>inspect_brokenframe_broken</t>
+  </si>
+  <si>
+    <t>연구원이 웃고 있는 듯한 모습이지만,
+말라붙은 혈흔과 깨진 파편 때문에 사진이 손상돼서 알아볼 수 없다.</t>
+  </si>
+  <si>
+    <t>inspect_manquarters_cabinet_glassfragments</t>
+  </si>
+  <si>
+    <t>유리 파편이 흩어져 있다. 액자가 부서진 조각인가?</t>
+  </si>
+  <si>
+    <t>inspect_manquarters_noticeboard_dailytimetable</t>
+  </si>
+  <si>
+    <t>연구원들의 하루 일과가 적혀 있다.</t>
+  </si>
+  <si>
+    <t>inspect_idcard_start</t>
+  </si>
+  <si>
+    <t>군인에게 지급받은 ID 카드다.
+카드에 마우스를 올려 조사할 수 있는 부분을 찾아보자.</t>
+  </si>
+  <si>
+    <t>inspect_idcard_portrait</t>
+  </si>
+  <si>
+    <t>내 프로필 사진이다.</t>
+  </si>
+  <si>
+    <t>inspect_idcard_projectname</t>
+  </si>
+  <si>
+    <t>Project DNAM. 'DNA MUTATION PROJECT'의 줄임말이다.&lt;np&gt;DNA를 조작해서 생체 병기를 만드는 프로젝트라니. 악취미가 따로 없군.</t>
+  </si>
+  <si>
+    <t>inspect_idcard_nametag</t>
+  </si>
+  <si>
+    <t>한재혁. 내 이름이다. 이곳의 수석 연구원이자 프로젝트 책임자로 발령받았다.&lt;np&gt;...뭐 그래봤자 이곳에 실제로 근무하는 건 나밖에 없지만.</t>
+  </si>
+  <si>
+    <t>inspect_idcard_barcode</t>
+  </si>
+  <si>
+    <t>이 바코드를 문의 단말에 태그하면 문이 열리는 구조로 되어 있다.</t>
+  </si>
+  <si>
+    <t>inspect_manquarters_noticeboard_mapprint</t>
+  </si>
+  <si>
+    <t>연구소의 자세한 구조가 그려져 있는 지도다.&lt;np&gt;지도를 외워서 좀 더 편하게 돌아다닐 수 있다.
+제 M을 눌러 미니맵을 열고 이동할 수 있다.</t>
+  </si>
+  <si>
+    <t>inspect_manquarters_noticeboard_experimentalrecord</t>
+  </si>
+  <si>
+    <t>DNA변이 바이러스의 실험 기록이다.&lt;np&gt;끔찍한 동물 실험 내용이 사진과 함께 적혀 있다.</t>
   </si>
 </sst>
 </file>
@@ -137,7 +200,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -145,6 +208,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -314,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="37.5" customWidth="1"/>
@@ -369,6 +435,86 @@
         <v>11</v>
       </c>
     </row>
+    <row r="7" spans="1:2" ht="33.75">
+      <c r="A7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="33.75">
+      <c r="A8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="33.75">
+      <c r="A9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="33.75">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="33.75">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="33.75">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="33.75">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="33.75">
+      <c r="A16" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
